--- a/results/reports/latest/summary.xlsx
+++ b/results/reports/latest/summary.xlsx
@@ -2459,82 +2459,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="C2" t="n">
         <v>0.0023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="E2" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.0031</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.0037</v>
+        <v>0.0038</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0073</v>
+        <v>0.0081</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0083</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0179</v>
+        <v>0.0173</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0227</v>
+        <v>0.0208</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0375</v>
+        <v>0.0354</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0617</v>
+        <v>0.0611</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0878</v>
+        <v>0.0872</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.068</v>
+        <v>0.0731</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0788</v>
+        <v>0.0924</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0772</v>
+        <v>0.0931</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1163</v>
+        <v>0.1129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1412</v>
+        <v>0.1465</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1803</v>
+        <v>0.1857</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2205</v>
+        <v>0.2333</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2792</v>
+        <v>0.3059</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3332</v>
+        <v>0.3538</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.2068</v>
+        <v>1.3041</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.2484</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="3">
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0033</v>
+        <v>0.0032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0029</v>
+        <v>0.0021</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="F3" t="n">
         <v>0.0031</v>
@@ -2562,64 +2562,64 @@
         <v>0.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0057</v>
+        <v>0.0062</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0059</v>
+        <v>0.0058</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0098</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0159</v>
+        <v>0.016</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0215</v>
+        <v>0.0202</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0323</v>
+        <v>0.0325</v>
       </c>
       <c r="O3" t="n">
-        <v>0.056</v>
+        <v>0.0563</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0819</v>
+        <v>0.0784</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0877</v>
+        <v>0.0912</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0953</v>
+        <v>0.091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0873</v>
+        <v>0.0833</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1143</v>
+        <v>0.1057</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1349</v>
+        <v>0.131</v>
       </c>
       <c r="V3" t="n">
-        <v>0.172</v>
+        <v>0.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.22</v>
+        <v>0.1895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2627</v>
+        <v>0.2467</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3622</v>
+        <v>0.3164</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.3206</v>
+        <v>1.3032</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.3503</v>
+        <v>1.2997</v>
       </c>
     </row>
     <row r="4">
@@ -2629,82 +2629,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0029</v>
+        <v>0.0024</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0027</v>
+        <v>0.0023</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003</v>
+        <v>0.0031</v>
       </c>
       <c r="E4" t="n">
         <v>0.0032</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0031</v>
+        <v>0.0034</v>
       </c>
       <c r="G4" t="n">
         <v>0.0035</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0065</v>
+        <v>0.0056</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0062</v>
+        <v>0.006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0103</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0101</v>
+        <v>0.0106</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0174</v>
+        <v>0.0173</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0256</v>
+        <v>0.0231</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0366</v>
+        <v>0.0346</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0659</v>
+        <v>0.0622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1023</v>
+        <v>0.1025</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1148</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1198</v>
+        <v>0.1149</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1348</v>
+        <v>0.1278</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1677</v>
+        <v>0.1741</v>
       </c>
       <c r="V4" t="n">
         <v>0.2219</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3104</v>
+        <v>0.3191</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3633</v>
+        <v>0.3559</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8618</v>
+        <v>0.7563</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.9352</v>
+        <v>7.5973</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.0494</v>
+        <v>7.7646</v>
       </c>
     </row>
     <row r="5">
@@ -2717,79 +2717,79 @@
         <v>0.0026</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0035</v>
+        <v>0.0036</v>
       </c>
       <c r="G5" t="n">
         <v>0.0038</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0069</v>
+        <v>0.007</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0108</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0107</v>
+        <v>0.0103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.019</v>
+        <v>0.0177</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0256</v>
+        <v>0.02</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0381</v>
+        <v>0.037</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0636</v>
+        <v>0.0625</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0969</v>
+        <v>0.0956</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1067</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1109</v>
+        <v>0.1108</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1069</v>
+        <v>0.1036</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1267</v>
+        <v>0.1098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1636</v>
+        <v>0.1507</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2046</v>
+        <v>0.1921</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2475</v>
+        <v>0.2251</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3243</v>
+        <v>0.3107</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4127</v>
+        <v>0.4211</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6096</v>
+        <v>1.4221</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6251</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="6">
@@ -2799,82 +2799,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="D6" t="n">
         <v>0.0032</v>
       </c>
       <c r="E6" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.0037</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.0033</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.0039</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0074</v>
+        <v>0.0076</v>
       </c>
       <c r="I6" t="n">
         <v>0.0072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0109</v>
+        <v>0.0101</v>
       </c>
       <c r="K6" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0195</v>
+        <v>0.018</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0286</v>
+        <v>0.024</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0396</v>
+        <v>0.0377</v>
       </c>
       <c r="O6" t="n">
-        <v>0.065</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0924</v>
+        <v>0.0838</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1105</v>
+        <v>0.1106</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1145</v>
+        <v>0.0939</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1143</v>
+        <v>0.1213</v>
       </c>
       <c r="U6" t="n">
-        <v>0.149</v>
+        <v>0.163</v>
       </c>
       <c r="V6" t="n">
-        <v>0.202</v>
+        <v>0.1994</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2489</v>
+        <v>0.2593</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2902</v>
+        <v>0.2847</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3625</v>
+        <v>0.3722</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.2658</v>
+        <v>1.3284</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3005</v>
+        <v>1.3875</v>
       </c>
     </row>
     <row r="7">
@@ -2884,82 +2884,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0028</v>
+        <v>0.0022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0037</v>
+        <v>0.0032</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0032</v>
+        <v>0.0035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0078</v>
+        <v>0.0074</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0071</v>
+        <v>0.007</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0114</v>
+        <v>0.0105</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0095</v>
+        <v>0.0111</v>
       </c>
       <c r="L7" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0252</v>
+        <v>0.0236</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0369</v>
+        <v>0.0367</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0954</v>
+        <v>0.0901</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1067</v>
+        <v>0.0916</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1066</v>
+        <v>0.1064</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1111</v>
+        <v>0.1153</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1327</v>
+        <v>0.1224</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1581</v>
+        <v>0.1422</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2117</v>
+        <v>0.2033</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2505</v>
+        <v>0.246</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3066</v>
+        <v>0.3003</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.35</v>
+        <v>0.3544</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.141</v>
+        <v>1.2251</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.0866</v>
+        <v>1.1707</v>
       </c>
     </row>
     <row r="8">
@@ -2969,82 +2969,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0025</v>
+        <v>0.0028</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003</v>
+        <v>0.0031</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0032</v>
+        <v>0.0028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003</v>
+        <v>0.0031</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0064</v>
+        <v>0.0063</v>
       </c>
       <c r="I8" t="n">
         <v>0.006</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0094</v>
+        <v>0.0078</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0162</v>
+        <v>0.0153</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0214</v>
+        <v>0.0193</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0325</v>
+        <v>0.032</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0583</v>
+        <v>0.0544</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0801</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0984</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0858</v>
+        <v>0.0944</v>
       </c>
       <c r="T8" t="n">
-        <v>0.106</v>
+        <v>0.1054</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1451</v>
+        <v>0.1484</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1637</v>
+        <v>0.1591</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2127</v>
+        <v>0.2074</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2524</v>
+        <v>0.2442</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2917</v>
+        <v>0.2874</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.0102</v>
+        <v>0.9866</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1286</v>
+        <v>1.0161</v>
       </c>
     </row>
     <row r="9">
@@ -3054,82 +3054,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0028</v>
+        <v>0.0022</v>
       </c>
       <c r="D9" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.0031</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.0037</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0038</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.0068</v>
+        <v>0.0065</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0069</v>
+        <v>0.0067</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0107</v>
+        <v>0.0095</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0105</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0186</v>
+        <v>0.017</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0222</v>
+        <v>0.0195</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0376</v>
+        <v>0.0361</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0623</v>
+        <v>0.0612</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0887</v>
+        <v>0.0819</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1028</v>
+        <v>0.0775</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0786</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0977</v>
+        <v>0.09</v>
       </c>
       <c r="T9" t="n">
-        <v>0.118</v>
+        <v>0.1181</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1715</v>
+        <v>0.1586</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2053</v>
+        <v>0.164</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2624</v>
+        <v>0.2289</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3096</v>
+        <v>0.2359</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3837</v>
+        <v>0.2909</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3159</v>
+        <v>0.6973</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3129</v>
+        <v>0.7262</v>
       </c>
     </row>
     <row r="10">
@@ -3139,82 +3139,82 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0025</v>
+        <v>0.0021</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="G10" t="n">
         <v>0.0038</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0071</v>
+        <v>0.0077</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0104</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0097</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0181</v>
+        <v>0.0175</v>
       </c>
       <c r="M10" t="n">
-        <v>0.025</v>
+        <v>0.0207</v>
       </c>
       <c r="N10" t="n">
-        <v>0.036</v>
+        <v>0.0364</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0615</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0888</v>
+        <v>0.0906</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0858</v>
+        <v>0.102</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1104</v>
+        <v>0.1065</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1068</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1196</v>
+        <v>0.1174</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1509</v>
+        <v>0.1389</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1842</v>
+        <v>0.2003</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2249</v>
+        <v>0.2322</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2753</v>
+        <v>0.3028</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3584</v>
+        <v>0.3758</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2335</v>
+        <v>1.4097</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.2498</v>
+        <v>1.4335</v>
       </c>
     </row>
     <row r="11">
@@ -3224,82 +3224,82 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0023</v>
+        <v>0.0021</v>
       </c>
       <c r="C11" t="n">
         <v>0.0022</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0031</v>
+        <v>0.0027</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0031</v>
+        <v>0.0029</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0034</v>
+        <v>0.0032</v>
       </c>
       <c r="G11" t="n">
         <v>0.0037</v>
       </c>
       <c r="H11" t="n">
-        <v>0.007</v>
+        <v>0.0071</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0066</v>
+        <v>0.0069</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0094</v>
+        <v>0.0086</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0105</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0176</v>
+        <v>0.0169</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0214</v>
+        <v>0.0198</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0377</v>
+        <v>0.0361</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0624</v>
+        <v>0.0602</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0804</v>
+        <v>0.0824</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0856</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0984</v>
+        <v>0.1036</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1023</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1021</v>
+        <v>0.0979</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1668</v>
+        <v>0.1517</v>
       </c>
       <c r="V11" t="n">
-        <v>0.196</v>
+        <v>0.1829</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2589</v>
+        <v>0.2465</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2936</v>
+        <v>0.2726</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3874</v>
+        <v>0.3745</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3674</v>
+        <v>1.3368</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.371</v>
+        <v>1.3171</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3375,7 @@
         <v>1.5647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1104</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="3">
@@ -3397,7 +3397,7 @@
         <v>1.6069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1075</v>
+        <v>0.1019</v>
       </c>
     </row>
     <row r="4">
@@ -3419,7 +3419,7 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.224</v>
+        <v>0.2078</v>
       </c>
     </row>
     <row r="5">
@@ -3441,7 +3441,7 @@
         <v>1.4199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1273</v>
+        <v>0.1187</v>
       </c>
     </row>
     <row r="6">
@@ -3463,7 +3463,7 @@
         <v>1.47</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1178</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="7">
@@ -3485,7 +3485,7 @@
         <v>1.4326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1205</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="8">
@@ -3507,7 +3507,7 @@
         <v>1.5876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1023</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="9">
@@ -3529,7 +3529,7 @@
         <v>1.4791</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1222</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="10">
@@ -3551,7 +3551,7 @@
         <v>0.9983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1127</v>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="11">
@@ -3573,7 +3573,7 @@
         <v>1.5508</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1179</v>
+        <v>0.1117</v>
       </c>
     </row>
   </sheetData>

--- a/results/reports/latest/summary.xlsx
+++ b/results/reports/latest/summary.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2100</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="4">
@@ -2459,82 +2459,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0018</v>
+        <v>0.0022</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0023</v>
+        <v>0.0025</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003</v>
+        <v>0.0031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0034</v>
+        <v>0.0035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0032</v>
+        <v>0.0035</v>
       </c>
       <c r="G2" t="n">
         <v>0.0038</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0081</v>
+        <v>0.0071</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0067</v>
+        <v>0.0071</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0121</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0106</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0173</v>
+        <v>0.0181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0208</v>
+        <v>0.0212</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0354</v>
+        <v>0.0371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0611</v>
+        <v>0.0658</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0872</v>
+        <v>0.0926</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0731</v>
+        <v>0.094</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0924</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0931</v>
+        <v>0.1029</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1129</v>
+        <v>0.1232</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1465</v>
+        <v>0.1651</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1857</v>
+        <v>0.2015</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2333</v>
+        <v>0.2497</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3059</v>
+        <v>0.3083</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3538</v>
+        <v>0.3919</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.3041</v>
+        <v>1.4621</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.332</v>
+        <v>1.4539</v>
       </c>
     </row>
     <row r="3">
@@ -2544,82 +2544,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0032</v>
+        <v>0.003</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0021</v>
+        <v>0.0025</v>
       </c>
       <c r="D3" t="n">
         <v>0.0031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003</v>
+        <v>0.0033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0031</v>
+        <v>0.0033</v>
       </c>
       <c r="G3" t="n">
         <v>0.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0062</v>
+        <v>0.0061</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0058</v>
+        <v>0.0064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0106</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="L3" t="n">
-        <v>0.016</v>
+        <v>0.0165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0202</v>
+        <v>0.0213</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0325</v>
+        <v>0.033</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0563</v>
+        <v>0.0603</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0784</v>
+        <v>0.077</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0912</v>
+        <v>0.0898</v>
       </c>
       <c r="R3" t="n">
-        <v>0.091</v>
+        <v>0.0936</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0833</v>
+        <v>0.073</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1057</v>
+        <v>0.1098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.131</v>
+        <v>0.1409</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1675</v>
+        <v>0.1815</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1895</v>
+        <v>0.2057</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2467</v>
+        <v>0.2632</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3164</v>
+        <v>0.3541</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.3032</v>
+        <v>1.287</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.2997</v>
+        <v>1.2885</v>
       </c>
     </row>
     <row r="4">
@@ -2629,82 +2629,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0023</v>
+        <v>0.0031</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="E4" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.0034</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.0035</v>
+        <v>0.0037</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0056</v>
+        <v>0.0062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006</v>
+        <v>0.0065</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0119</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0106</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0173</v>
+        <v>0.018</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0231</v>
+        <v>0.0269</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0346</v>
+        <v>0.0374</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0622</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1013</v>
+        <v>0.0994</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1025</v>
+        <v>0.1189</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.131</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1149</v>
+        <v>0.1191</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1278</v>
+        <v>0.1387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1741</v>
+        <v>0.1831</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2219</v>
+        <v>0.2399</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3191</v>
+        <v>0.3463</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3559</v>
+        <v>0.3987</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7563</v>
+        <v>0.865</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5973</v>
+        <v>6.4057</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.7646</v>
+        <v>6.8328</v>
       </c>
     </row>
     <row r="5">
@@ -2714,82 +2714,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
       <c r="D5" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.0034</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.0036</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008</v>
+        <v>0.0075</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007</v>
+        <v>0.0073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0113</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0103</v>
+        <v>0.0107</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0177</v>
+        <v>0.0192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02</v>
+        <v>0.0216</v>
       </c>
       <c r="N5" t="n">
-        <v>0.037</v>
+        <v>0.0383</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0625</v>
+        <v>0.0669</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0956</v>
+        <v>0.0977</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1067</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1108</v>
+        <v>0.1107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1036</v>
+        <v>0.1018</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1098</v>
+        <v>0.1201</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1507</v>
+        <v>0.1508</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1921</v>
+        <v>0.2081</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2251</v>
+        <v>0.24</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3107</v>
+        <v>0.3145</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4211</v>
+        <v>0.3885</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.4221</v>
+        <v>1.4537</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.431</v>
+        <v>1.4427</v>
       </c>
     </row>
     <row r="6">
@@ -2799,82 +2799,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0022</v>
+        <v>0.0027</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0032</v>
+        <v>0.0037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0035</v>
+        <v>0.0036</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0037</v>
+        <v>0.0033</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004</v>
+        <v>0.0041</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0072</v>
+        <v>0.0077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0101</v>
+        <v>0.0134</v>
       </c>
       <c r="K6" t="n">
-        <v>0.012</v>
+        <v>0.0128</v>
       </c>
       <c r="L6" t="n">
-        <v>0.018</v>
+        <v>0.0201</v>
       </c>
       <c r="M6" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0377</v>
+        <v>0.0388</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0838</v>
+        <v>0.0958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0999</v>
+        <v>0.1113</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1106</v>
+        <v>0.1025</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0939</v>
+        <v>0.1027</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1213</v>
+        <v>0.1316</v>
       </c>
       <c r="U6" t="n">
-        <v>0.163</v>
+        <v>0.175</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1994</v>
+        <v>0.2157</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2593</v>
+        <v>0.2715</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2847</v>
+        <v>0.2989</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3722</v>
+        <v>0.3909</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.3284</v>
+        <v>1.2044</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3875</v>
+        <v>1.2325</v>
       </c>
     </row>
     <row r="7">
@@ -2887,79 +2887,79 @@
         <v>0.0028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0022</v>
+        <v>0.0026</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0034</v>
+        <v>0.0031</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0032</v>
+        <v>0.0033</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0035</v>
+        <v>0.0037</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0038</v>
+        <v>0.004</v>
       </c>
       <c r="H7" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.0074</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.007</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.0105</v>
+        <v>0.0121</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0111</v>
+        <v>0.0113</v>
       </c>
       <c r="L7" t="n">
-        <v>0.018</v>
+        <v>0.0194</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0236</v>
+        <v>0.0226</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0367</v>
+        <v>0.039</v>
       </c>
       <c r="O7" t="n">
-        <v>0.062</v>
+        <v>0.065</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0901</v>
+        <v>0.0978</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0916</v>
+        <v>0.1065</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1064</v>
+        <v>0.1152</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1153</v>
+        <v>0.1159</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1224</v>
+        <v>0.1157</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1422</v>
+        <v>0.1585</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2033</v>
+        <v>0.2048</v>
       </c>
       <c r="W7" t="n">
-        <v>0.246</v>
+        <v>0.2579</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3003</v>
+        <v>0.3158</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3544</v>
+        <v>0.3873</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.2251</v>
+        <v>1.7146</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.1707</v>
+        <v>1.8538</v>
       </c>
     </row>
     <row r="8">
@@ -2969,82 +2969,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="D8" t="n">
         <v>0.0031</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0028</v>
+        <v>0.0034</v>
       </c>
       <c r="F8" t="n">
         <v>0.0031</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0034</v>
+        <v>0.0037</v>
       </c>
       <c r="H8" t="n">
         <v>0.0063</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006</v>
+        <v>0.0063</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0078</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0153</v>
+        <v>0.0164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0193</v>
+        <v>0.0192</v>
       </c>
       <c r="N8" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0544</v>
+        <v>0.0588</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0856</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0829</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0944</v>
+        <v>0.1022</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1054</v>
+        <v>0.111</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1484</v>
+        <v>0.154</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1591</v>
+        <v>0.1851</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2074</v>
+        <v>0.232</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2442</v>
+        <v>0.2883</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2874</v>
+        <v>0.3503</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9866</v>
+        <v>1.3126</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.0161</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="9">
@@ -3054,82 +3054,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0022</v>
+        <v>0.0026</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0022</v>
+        <v>0.0027</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0032</v>
+        <v>0.0036</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0031</v>
+        <v>0.0033</v>
       </c>
       <c r="F9" t="n">
         <v>0.0032</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0037</v>
+        <v>0.0039</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0065</v>
+        <v>0.0062</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0067</v>
+        <v>0.007</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0095</v>
+        <v>0.0104</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0104</v>
       </c>
       <c r="L9" t="n">
-        <v>0.017</v>
+        <v>0.0183</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0195</v>
+        <v>0.0218</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0361</v>
+        <v>0.038</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0612</v>
+        <v>0.0668</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0819</v>
+        <v>0.0945</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0775</v>
+        <v>0.0789</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0786</v>
+        <v>0.0901</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09</v>
+        <v>0.1024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1181</v>
+        <v>0.1152</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1586</v>
+        <v>0.1524</v>
       </c>
       <c r="V9" t="n">
-        <v>0.164</v>
+        <v>0.1732</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2289</v>
+        <v>0.2303</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2359</v>
+        <v>0.255</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2909</v>
+        <v>0.3249</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6973</v>
+        <v>1.0615</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7262</v>
+        <v>1.0658</v>
       </c>
     </row>
     <row r="10">
@@ -3139,82 +3139,82 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002</v>
+        <v>0.0023</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0021</v>
+        <v>0.0027</v>
       </c>
       <c r="D10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.0034</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0036</v>
-      </c>
       <c r="G10" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0077</v>
+        <v>0.0073</v>
       </c>
       <c r="I10" t="n">
         <v>0.0068</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0121</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0104</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0207</v>
+        <v>0.0213</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0615</v>
+        <v>0.0672</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0906</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.102</v>
+        <v>0.1152</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1065</v>
+        <v>0.1021</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1068</v>
+        <v>0.1023</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1174</v>
+        <v>0.1304</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1389</v>
+        <v>0.1684</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2003</v>
+        <v>0.2176</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2322</v>
+        <v>0.2624</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3028</v>
+        <v>0.3364</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3758</v>
+        <v>0.4044</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4097</v>
+        <v>1.5379</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4335</v>
+        <v>1.5382</v>
       </c>
     </row>
     <row r="11">
@@ -3224,82 +3224,82 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0022</v>
+        <v>0.0023</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0027</v>
+        <v>0.0031</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0029</v>
+        <v>0.0036</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0032</v>
+        <v>0.0034</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0037</v>
+        <v>0.0039</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0071</v>
+        <v>0.007</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0069</v>
+        <v>0.007</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0086</v>
+        <v>0.0111</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0105</v>
+        <v>0.0104</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0169</v>
+        <v>0.0185</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0198</v>
+        <v>0.0204</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0361</v>
+        <v>0.0379</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0602</v>
+        <v>0.0636</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0824</v>
+        <v>0.0917</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0877</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1036</v>
+        <v>0.0897</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0979</v>
+        <v>0.1163</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1517</v>
+        <v>0.1468</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1829</v>
+        <v>0.1781</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2465</v>
+        <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2726</v>
+        <v>0.2698</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3745</v>
+        <v>0.3158</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3368</v>
+        <v>1.0933</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3171</v>
+        <v>1.1557</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3375,7 @@
         <v>1.5647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1151</v>
+        <v>0.1232</v>
       </c>
     </row>
     <row r="3">
@@ -3397,7 +3397,7 @@
         <v>1.6069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1019</v>
+        <v>0.1071</v>
       </c>
     </row>
     <row r="4">
@@ -3419,7 +3419,7 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2078</v>
+        <v>0.2056</v>
       </c>
     </row>
     <row r="5">
@@ -3441,7 +3441,7 @@
         <v>1.4199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1187</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="6">
@@ -3463,7 +3463,7 @@
         <v>1.47</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1192</v>
+        <v>0.1248</v>
       </c>
     </row>
     <row r="7">
@@ -3485,7 +3485,7 @@
         <v>1.4326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1168</v>
+        <v>0.1281</v>
       </c>
     </row>
     <row r="8">
@@ -3507,7 +3507,7 @@
         <v>1.5876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0997</v>
+        <v>0.1135</v>
       </c>
     </row>
     <row r="9">
@@ -3529,7 +3529,7 @@
         <v>1.4791</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1006</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="10">
@@ -3551,7 +3551,7 @@
         <v>0.9983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1178</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="11">
@@ -3573,7 +3573,7 @@
         <v>1.5508</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1117</v>
+        <v>0.1106</v>
       </c>
     </row>
   </sheetData>
@@ -3587,13 +3587,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3604,15 +3603,10 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>invalid</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
         <is>
           <t>example_problem</t>
         </is>
@@ -3625,16 +3619,9 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
         <v>2094</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3643,16 +3630,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" t="n">
         <v>2094</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3661,16 +3641,9 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
         <v>2094</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3679,16 +3652,9 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
         <v>2094</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3697,16 +3663,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" t="n">
         <v>2094</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3715,16 +3674,9 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
         <v>2094</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3733,16 +3685,9 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="n">
         <v>2094</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3751,16 +3696,9 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
         <v>2094</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3769,16 +3707,9 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" t="n">
         <v>2094</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3787,16 +3718,9 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="n">
         <v>2094</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>no schedule table found in output</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
